--- a/Тесты.xlsx
+++ b/Тесты.xlsx
@@ -5,30 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rufus\Desktop\6 семестр\Мои работы\Методы Оптимизации - Лабы\MO2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rufus\Desktop\Repositories\Python\MO_Pt2\NSTU_MO_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABA0A4B0-531A-4948-B69A-1C4A4C5165EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5DB211-5630-471A-939D-440386A1B12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{098766AF-C197-4C7E-BDEC-25F5D126499E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{098766AF-C197-4C7E-BDEC-25F5D126499E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -38,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="44">
   <si>
     <t>Точность</t>
   </si>
@@ -164,6 +155,12 @@
   </si>
   <si>
     <t>0.01806405]</t>
+  </si>
+  <si>
+    <t>Н</t>
+  </si>
+  <si>
+    <t>Б</t>
   </si>
 </sst>
 </file>
@@ -372,33 +369,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -423,12 +399,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -461,9 +431,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -476,46 +443,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -546,6 +477,87 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -630,8 +642,8 @@
       <xdr:rowOff>4011</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="440698" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -673,6 +685,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -755,7 +768,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -819,8 +832,8 @@
       <xdr:rowOff>1003</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="522387" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -862,6 +875,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -950,7 +964,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="12" name="TextBox 11">
@@ -1014,8 +1028,8 @@
       <xdr:rowOff>29889</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="663900" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -1057,6 +1071,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1145,7 +1160,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -1209,8 +1224,8 @@
       <xdr:rowOff>28247</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="625684" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -1252,6 +1267,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1340,7 +1356,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="TextBox 13">
@@ -1404,8 +1420,8 @@
       <xdr:rowOff>13138</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="662104" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -1447,6 +1463,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1535,7 +1552,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="TextBox 14">
@@ -1599,8 +1616,8 @@
       <xdr:rowOff>4011</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="440698" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -1642,6 +1659,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1724,7 +1742,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -1788,8 +1806,8 @@
       <xdr:rowOff>1003</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="522387" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="TextBox 21">
@@ -1831,6 +1849,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1919,7 +1938,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="22" name="TextBox 21">
@@ -1983,8 +2002,8 @@
       <xdr:rowOff>29889</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="663900" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="TextBox 22">
@@ -2026,6 +2045,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2114,7 +2134,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="23" name="TextBox 22">
@@ -2178,8 +2198,8 @@
       <xdr:rowOff>28247</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="625684" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="TextBox 23">
@@ -2221,6 +2241,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2309,7 +2330,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="24" name="TextBox 23">
@@ -2373,8 +2394,8 @@
       <xdr:rowOff>13138</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="662104" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="TextBox 24">
@@ -2416,6 +2437,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2504,7 +2526,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="25" name="TextBox 24">
@@ -2568,8 +2590,8 @@
       <xdr:rowOff>4011</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="440698" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -2611,6 +2633,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2693,7 +2716,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="26" name="TextBox 25">
@@ -2757,8 +2780,8 @@
       <xdr:rowOff>1003</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="522387" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="27" name="TextBox 26">
@@ -2800,6 +2823,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2888,7 +2912,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="27" name="TextBox 26">
@@ -2952,8 +2976,8 @@
       <xdr:rowOff>29889</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="663900" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="28" name="TextBox 27">
@@ -2995,6 +3019,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -3083,7 +3108,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="28" name="TextBox 27">
@@ -3147,8 +3172,8 @@
       <xdr:rowOff>28247</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="625684" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="29" name="TextBox 28">
@@ -3190,6 +3215,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -3278,7 +3304,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="29" name="TextBox 28">
@@ -3342,8 +3368,8 @@
       <xdr:rowOff>13138</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="662104" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="30" name="TextBox 29">
@@ -3385,6 +3411,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -3473,7 +3500,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="30" name="TextBox 29">
@@ -3537,8 +3564,8 @@
       <xdr:rowOff>4011</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="440698" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -3580,6 +3607,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -3662,7 +3690,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -3726,8 +3754,8 @@
       <xdr:rowOff>1003</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="522387" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -3769,6 +3797,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -3857,7 +3886,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="32" name="TextBox 31">
@@ -3921,8 +3950,8 @@
       <xdr:rowOff>29889</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="663900" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -3964,6 +3993,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -4052,7 +4082,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -4116,8 +4146,8 @@
       <xdr:rowOff>28247</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="625684" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="34" name="TextBox 33">
@@ -4159,6 +4189,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -4247,7 +4278,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="34" name="TextBox 33">
@@ -4311,8 +4342,8 @@
       <xdr:rowOff>13138</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="662104" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="35" name="TextBox 34">
@@ -4354,6 +4385,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -4442,7 +4474,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="35" name="TextBox 34">
@@ -4798,603 +4830,615 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC9AB0E-F2EB-4B0E-9E38-0A1BC4764938}">
-  <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="17"/>
-    <col min="2" max="2" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="9.109375" style="10"/>
+    <col min="2" max="2" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1">
         <v>5</v>
       </c>
-      <c r="I1" s="6">
+      <c r="I1" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="20" t="s">
+      <c r="J1" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="38"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="28"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="F2" s="45"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="4">
+        <v>7</v>
+      </c>
+      <c r="C3" s="24">
+        <v>586</v>
+      </c>
+      <c r="D3" s="27">
+        <v>1.00424307</v>
+      </c>
+      <c r="E3" s="21">
+        <v>1.0042647</v>
+      </c>
+      <c r="F3" s="21">
+        <v>1.8050449799999999E-5</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4">
+        <v>8</v>
+      </c>
+      <c r="C4" s="24">
+        <v>672</v>
+      </c>
+      <c r="D4" s="27">
+        <v>1.00051063</v>
+      </c>
+      <c r="E4" s="21">
+        <v>1.00038297</v>
+      </c>
+      <c r="F4" s="21">
+        <v>1.8904964899999999E-6</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4">
+        <v>9</v>
+      </c>
+      <c r="C5" s="24">
+        <v>754</v>
+      </c>
+      <c r="D5" s="27">
+        <v>1.00044439</v>
+      </c>
+      <c r="E5" s="21">
+        <v>1.0004466599999999</v>
+      </c>
+      <c r="F5" s="21">
+        <v>1.98000096E-7</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <v>10</v>
+      </c>
+      <c r="C6" s="24">
+        <v>840</v>
+      </c>
+      <c r="D6" s="27">
+        <v>1.00005495</v>
+      </c>
+      <c r="E6" s="21">
+        <v>1.0000414099999999</v>
+      </c>
+      <c r="F6" s="21">
+        <v>2.1351759499999999E-8</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>11</v>
+      </c>
+      <c r="C7" s="8">
+        <v>922</v>
+      </c>
+      <c r="D7" s="28">
+        <v>1.0000479200000001</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1.0000481699999999</v>
+      </c>
+      <c r="F7" s="19">
+        <v>2.3025232300000001E-9</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="J9" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="38"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5">
+      <c r="B11" s="4">
+        <v>5</v>
+      </c>
+      <c r="C11" s="24">
         <v>427</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D11" s="27">
         <v>1.0004447000000001</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E11" s="21">
         <v>1.00044697</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F11" s="21">
         <v>1.9827172199999999E-7</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B12" s="4">
         <v>5</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C12" s="24">
         <v>427</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D12" s="27">
         <v>1.0004447000000001</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E12" s="21">
         <v>1.00044697</v>
       </c>
-      <c r="F4" s="23">
-        <v>1.00044697</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="F12" s="21">
+        <v>1.9827172199999999E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B13" s="4">
         <v>6</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C13" s="24">
         <v>513</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D13" s="27">
         <v>1.00004705</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E13" s="21">
         <v>1.0000472899999999</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F13" s="21">
         <v>2.21935692E-9</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B14" s="4">
         <v>6</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C14" s="24">
         <v>513</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D14" s="27">
         <v>1.00004705</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E14" s="21">
         <v>1.0000472899999999</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F14" s="21">
         <v>2.21935692E-9</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B15" s="7">
         <v>7</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C15" s="8">
         <v>599</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D15" s="28">
         <v>1.0000049799999999</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E15" s="19">
         <v>1.000005</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F15" s="19">
         <v>2.4841118000000001E-11</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    </row>
+    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B17" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C17" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D17" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19" t="s">
+      <c r="E17" s="44"/>
+      <c r="F17" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="20" t="s">
+      <c r="H17" s="2">
+        <v>9</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="38"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E18" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="28"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="F18" s="45"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B19" s="4">
+        <v>11</v>
+      </c>
+      <c r="C19" s="24">
+        <v>922</v>
+      </c>
+      <c r="D19" s="27">
+        <v>1.01034234</v>
+      </c>
+      <c r="E19" s="21">
+        <v>1.0103957699999999</v>
+      </c>
+      <c r="F19" s="21">
+        <v>1.07249496E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="4">
+        <v>12</v>
+      </c>
+      <c r="C20" s="24">
+        <v>1008</v>
+      </c>
+      <c r="D20" s="27">
+        <v>1.0030845500000001</v>
+      </c>
+      <c r="E20" s="21">
+        <v>1.00263737</v>
+      </c>
+      <c r="F20" s="21">
+        <v>2.9511907099999999E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5">
-        <v>586</v>
-      </c>
-      <c r="D11" s="22">
-        <v>1.00424307</v>
-      </c>
-      <c r="E11" s="23">
-        <v>1.0042647</v>
-      </c>
-      <c r="F11" s="23">
-        <v>1.8050449799999999E-5</v>
-      </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="B21" s="4">
+        <v>14</v>
+      </c>
+      <c r="C21" s="24">
+        <v>1176</v>
+      </c>
+      <c r="D21" s="27">
+        <v>1.00085245</v>
+      </c>
+      <c r="E21" s="21">
+        <v>1.0007292299999999</v>
+      </c>
+      <c r="F21" s="21">
+        <v>2.2447934100000001E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="4">
+        <v>16</v>
+      </c>
+      <c r="C22" s="24">
+        <v>1344</v>
+      </c>
+      <c r="D22" s="27">
+        <v>1.00023459</v>
+      </c>
+      <c r="E22" s="21">
+        <v>1.00020058</v>
+      </c>
+      <c r="F22" s="21">
+        <v>1.7072499800000001E-7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8">
+        <v>1512</v>
+      </c>
+      <c r="D23" s="28">
+        <v>1.0000648000000001</v>
+      </c>
+      <c r="E23" s="19">
+        <v>1.00005543</v>
+      </c>
+      <c r="F23" s="19">
+        <v>1.2977938999999999E-8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="38"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="45"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="4">
+        <v>7</v>
+      </c>
+      <c r="C27" s="24">
+        <v>599</v>
+      </c>
+      <c r="D27" s="27">
+        <v>1.0028499099999999</v>
+      </c>
+      <c r="E27" s="21">
+        <v>1.0028646400000001</v>
+      </c>
+      <c r="F27" s="21">
+        <v>8.1436982300000002E-6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B28" s="4">
+        <v>7</v>
+      </c>
+      <c r="C28" s="24">
+        <v>599</v>
+      </c>
+      <c r="D28" s="27">
+        <v>1.0028499099999999</v>
+      </c>
+      <c r="E28" s="21">
+        <v>1.0028646400000001</v>
+      </c>
+      <c r="F28" s="21">
+        <v>8.1436982300000002E-6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>672</v>
-      </c>
-      <c r="D12" s="22">
-        <v>1.00051063</v>
-      </c>
-      <c r="E12" s="23">
-        <v>1.00038297</v>
-      </c>
-      <c r="F12" s="23">
-        <v>1.8904964899999999E-6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="11">
+      <c r="C29" s="24">
+        <v>685</v>
+      </c>
+      <c r="D29" s="27">
+        <v>1.00078588</v>
+      </c>
+      <c r="E29" s="21">
+        <v>1.00078994</v>
+      </c>
+      <c r="F29" s="21">
+        <v>6.1925179099999997E-7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="4">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>754</v>
-      </c>
-      <c r="D13" s="22">
-        <v>1.00044439</v>
-      </c>
-      <c r="E13" s="23">
-        <v>1.0004466599999999</v>
-      </c>
-      <c r="F13" s="23">
-        <v>1.98000096E-7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="11">
+      <c r="C30" s="24">
+        <v>771</v>
+      </c>
+      <c r="D30" s="27">
+        <v>1.0002167099999999</v>
+      </c>
+      <c r="E30" s="21">
+        <v>1.00021783</v>
+      </c>
+      <c r="F30" s="21">
+        <v>4.7088173300000002E-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
         <v>10</v>
       </c>
-      <c r="C14" s="5">
-        <v>840</v>
-      </c>
-      <c r="D14" s="22">
-        <v>1.00005495</v>
-      </c>
-      <c r="E14" s="23">
-        <v>1.0000414099999999</v>
-      </c>
-      <c r="F14" s="23">
-        <v>2.1351759499999999E-8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="14">
-        <v>11</v>
-      </c>
-      <c r="C15" s="15">
-        <v>922</v>
-      </c>
-      <c r="D15" s="24">
-        <v>1.0000479200000001</v>
-      </c>
-      <c r="E15" s="25">
-        <v>1.0000481699999999</v>
-      </c>
-      <c r="F15" s="25">
-        <v>2.3025232300000001E-9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="6">
-        <v>5</v>
-      </c>
-      <c r="I17" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="28"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="11">
-        <v>4</v>
-      </c>
-      <c r="C19" s="5">
-        <v>341</v>
-      </c>
-      <c r="D19" s="22">
-        <v>1.00004425</v>
-      </c>
-      <c r="E19" s="23">
-        <v>1.0000444799999999</v>
-      </c>
-      <c r="F19" s="23">
-        <v>1.9633269799999999E-9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="11">
-        <v>4</v>
-      </c>
-      <c r="C20" s="5">
-        <v>341</v>
-      </c>
-      <c r="D20" s="22">
-        <v>1.00004425</v>
-      </c>
-      <c r="E20" s="23">
-        <v>1.0000444799999999</v>
-      </c>
-      <c r="F20" s="23">
-        <v>1.9633269799999999E-9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="11">
-        <v>4</v>
-      </c>
-      <c r="C21" s="5">
-        <v>341</v>
-      </c>
-      <c r="D21" s="22">
-        <v>1.00004425</v>
-      </c>
-      <c r="E21" s="23">
-        <v>1.0000444799999999</v>
-      </c>
-      <c r="F21" s="23">
-        <v>1.9633269799999999E-9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="11">
-        <v>5</v>
-      </c>
-      <c r="C22" s="5">
-        <v>427</v>
-      </c>
-      <c r="D22" s="22">
-        <v>1.0000010800000001</v>
-      </c>
-      <c r="E22" s="23">
-        <v>1.00000109</v>
-      </c>
-      <c r="F22" s="23">
-        <v>1.1801274700000001E-12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="14">
-        <v>5</v>
-      </c>
-      <c r="C23" s="15">
-        <v>427</v>
-      </c>
-      <c r="D23" s="24">
-        <v>1.0000010800000001</v>
-      </c>
-      <c r="E23" s="25">
-        <v>1.00000109</v>
-      </c>
-      <c r="F23" s="25">
-        <v>1.1801274700000001E-12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="28"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="11">
-        <v>5</v>
-      </c>
-      <c r="C27" s="5">
-        <v>418</v>
-      </c>
-      <c r="D27" s="22">
-        <v>1.0008735099999999</v>
-      </c>
-      <c r="E27" s="23">
-        <v>1.00087791</v>
-      </c>
-      <c r="F27" s="23">
-        <v>7.6495700699999998E-7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="11">
-        <v>5</v>
-      </c>
-      <c r="C28" s="5">
-        <v>418</v>
-      </c>
-      <c r="D28" s="22">
-        <v>1.0008735099999999</v>
-      </c>
-      <c r="E28" s="23">
-        <v>1.00087791</v>
-      </c>
-      <c r="F28" s="23">
-        <v>7.6495700699999998E-7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="11">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>504</v>
-      </c>
-      <c r="D29" s="22">
-        <v>1.00001681</v>
-      </c>
-      <c r="E29" s="23">
-        <v>1.0000068099999999</v>
-      </c>
-      <c r="F29" s="23">
-        <v>1.02788586E-8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="11">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>504</v>
-      </c>
-      <c r="D30" s="22">
-        <v>1.00001681</v>
-      </c>
-      <c r="E30" s="23">
-        <v>1.0000068099999999</v>
-      </c>
-      <c r="F30" s="23">
-        <v>1.02788586E-8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="14">
-        <v>7</v>
-      </c>
-      <c r="C31" s="15">
-        <v>586</v>
-      </c>
-      <c r="D31" s="24">
-        <v>1.0000117399999999</v>
-      </c>
-      <c r="E31" s="25">
-        <v>1.0000118</v>
-      </c>
-      <c r="F31" s="25">
-        <v>1.3811179799999999E-10</v>
+      <c r="C31" s="8">
+        <v>857</v>
+      </c>
+      <c r="D31" s="28">
+        <v>1.0000597600000001</v>
+      </c>
+      <c r="E31" s="19">
+        <v>1.00006007</v>
+      </c>
+      <c r="F31" s="19">
+        <v>3.5806100200000002E-9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5404,1435 +5448,1462 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C07E64-7C14-49F0-845C-FB0F44D8A6BF}">
   <dimension ref="A1:U59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="27" customWidth="1"/>
-    <col min="5" max="6" width="16" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="16" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="2" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="18" customWidth="1"/>
+    <col min="5" max="6" width="16" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="16" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="34"/>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="5"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="5"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="5"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="5"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="5"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="5"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="5"/>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="63"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="38"/>
-    </row>
-    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="32" t="s">
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="62"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="45"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="45" t="s">
+      <c r="B10" s="57"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="33" t="s">
+      <c r="F10" s="58"/>
+      <c r="G10" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="20"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="33" t="s">
+      <c r="H10" s="11"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="45" t="s">
+      <c r="L10" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="41"/>
-    </row>
-    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29">
+      <c r="M10" s="58"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="20">
         <v>1</v>
       </c>
-      <c r="B11" s="51">
+      <c r="B11" s="29">
         <v>4.4811460500000004</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="14">
         <v>4.4988980300000003</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="17">
         <v>12.1498911</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="29">
         <v>-208.00001700000001</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="14">
         <v>200.00001700000001</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="17">
         <v>2.4944899300000001E-3</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="13">
         <v>-0.51885394799999995</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="17">
         <v>0.49889802700000002</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11" s="13">
         <v>-103.850109</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="17">
         <v>1.5884248400000001</v>
       </c>
-      <c r="L11" s="51">
+      <c r="L11" s="29">
         <v>3.4118965399999999</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="14">
         <v>3.5503955299999999</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="39">
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="25">
         <v>2</v>
       </c>
-      <c r="B12" s="58">
+      <c r="B12" s="36">
         <v>1.43060436</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="12">
         <v>1.3245258099999999</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="26">
         <v>1.31068601</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="36">
         <v>-3.4118965399999999</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="12">
         <v>-3.5503955299999999</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="26">
         <v>0.89408973999999997</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="11">
         <v>-3.0505416900000002</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="26">
         <v>-3.17437222</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="11">
         <v>-10.839205099999999</v>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="26">
         <v>3.0832193600000002</v>
       </c>
-      <c r="L12" s="58">
+      <c r="L12" s="36">
         <v>22.076920699999999</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="12">
         <v>-21.215711899999999</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29">
+    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="20">
         <v>3</v>
       </c>
-      <c r="B13" s="51">
+      <c r="B13" s="29">
         <v>1.3755337000000001</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="14">
         <v>1.37744819</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="17">
         <v>0.141392088</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="29">
         <v>-22.076920699999999</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="14">
         <v>21.215711899999999</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="17">
         <v>2.4944899300000001E-3</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="13">
         <v>-5.5070656400000001E-2</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="17">
         <v>5.2922379499999998E-2</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="13">
         <v>-1.1692939200000001</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="17">
         <v>1.58999102</v>
       </c>
-      <c r="L13" s="51">
+      <c r="L13" s="29">
         <v>0.36817049400000001</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="14">
         <v>0.382897131</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="39">
+    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="25">
         <v>4</v>
       </c>
-      <c r="B14" s="58">
+      <c r="B14" s="36">
         <v>1.0451950299999999</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="12">
         <v>1.03389613</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="26">
         <v>1.48090993E-2</v>
       </c>
-      <c r="E14" s="58">
+      <c r="E14" s="36">
         <v>-0.36817049400000001</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="12">
         <v>-0.382897131</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="26">
         <v>0.89724375700000003</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="11">
         <v>-0.33033867700000002</v>
       </c>
-      <c r="I14" s="40">
+      <c r="I14" s="26">
         <v>-0.34355205999999999</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="11">
         <v>-0.12658298900000001</v>
       </c>
-      <c r="K14" s="40">
+      <c r="K14" s="26">
         <v>3.1165530800000001</v>
       </c>
-      <c r="L14" s="58">
+      <c r="L14" s="36">
         <v>2.3501698800000002</v>
       </c>
-      <c r="M14" s="21">
+      <c r="M14" s="12">
         <v>-2.2597796200000002</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="29">
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="20">
         <v>5</v>
       </c>
-      <c r="B15" s="51">
+      <c r="B15" s="29">
         <v>1.0393325499999999</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="14">
         <v>1.0395331299999999</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="17">
         <v>1.5510726600000001E-3</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="29">
         <v>-2.3501698800000002</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="14">
         <v>2.2597796200000002</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="17">
         <v>2.4944899300000001E-3</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="13">
         <v>-5.8624751000000003E-3</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="17">
         <v>5.6369975100000001E-3</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="13">
         <v>-1.32580266E-2</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="17">
         <v>1.59030498</v>
       </c>
-      <c r="L15" s="51">
+      <c r="L15" s="29">
         <v>3.8550219400000002E-2</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="14">
         <v>4.0115091399999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="39">
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="25">
         <v>6</v>
       </c>
-      <c r="B16" s="58">
+      <c r="B16" s="36">
         <v>1.0048653000000001</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="12">
         <v>1.0036667500000001</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="26">
         <v>1.6732497899999999E-4</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E16" s="36">
         <v>-3.8550219400000002E-2</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="12">
         <v>-4.0115091399999997E-2</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="26">
         <v>0.894086979</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="11">
         <v>-3.4467249200000001E-2</v>
       </c>
-      <c r="I16" s="40">
+      <c r="I16" s="26">
         <v>-3.58663808E-2</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="11">
         <v>-1.3837476799999999E-3</v>
       </c>
-      <c r="K16" s="40">
+      <c r="K16" s="26">
         <v>3.1211057599999998</v>
       </c>
-      <c r="L16" s="58">
+      <c r="L16" s="36">
         <v>0.24944206199999999</v>
       </c>
-      <c r="M16" s="21">
+      <c r="M16" s="12">
         <v>-0.23971125500000001</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="32">
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="22">
         <v>7</v>
       </c>
-      <c r="B17" s="52">
+      <c r="B17" s="30">
         <v>1.00424307</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="16">
         <v>1.0042647</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="23">
         <v>1.8050449799999999E-5</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="30">
         <v>-0.24944206199999999</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="16">
         <v>0.23971125500000001</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="23">
         <v>2.4944899300000001E-3</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="15">
         <v>-6.2223071099999996E-4</v>
       </c>
-      <c r="I17" s="33">
+      <c r="I17" s="23">
         <v>5.9795731100000004E-4</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="15">
         <v>-1.4927452899999999E-4</v>
       </c>
-      <c r="K17" s="33">
+      <c r="K17" s="23">
         <v>1.5906761</v>
       </c>
-      <c r="L17" s="52">
+      <c r="L17" s="30">
         <v>4.1599756599999997E-3</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="16">
         <v>4.3263696400000001E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="5"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="5"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="5"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="5"/>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="5"/>
-    </row>
-    <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="63"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="20"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-    </row>
-    <row r="25" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="45" t="s">
+      <c r="B25" s="57"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="41"/>
-      <c r="G25" s="40" t="s">
+      <c r="F25" s="58"/>
+      <c r="G25" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="40" t="s">
+      <c r="H25" s="11"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="L25" s="45" t="s">
+      <c r="L25" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="M25" s="41"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-    </row>
-    <row r="26" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="29">
+      <c r="M25" s="58"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="20">
         <v>1</v>
       </c>
-      <c r="B26" s="51">
+      <c r="B26" s="29">
         <v>2.0710685099999999</v>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="14">
         <v>4.2928375000000001</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="17">
         <v>1.1484216700000001</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="29">
         <v>-42008.010499999997</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="14">
         <v>4200.00288</v>
       </c>
-      <c r="G26" s="26">
+      <c r="G26" s="17">
         <v>6.9723165900000006E-5</v>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="13">
         <v>-2.9289314900000001</v>
       </c>
-      <c r="I26" s="26">
+      <c r="I26" s="17">
         <v>0.292837497</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26" s="13">
         <v>-44114.851600000002</v>
       </c>
-      <c r="K26" s="26">
+      <c r="K26" s="17">
         <v>1.9206537100000001</v>
       </c>
-      <c r="L26" s="51">
+      <c r="L26" s="29">
         <v>-0.76788308999999999</v>
       </c>
-      <c r="M26" s="23">
+      <c r="M26" s="14">
         <v>0.70254135799999995</v>
       </c>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="39">
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="25">
         <v>2</v>
       </c>
-      <c r="B27" s="58">
+      <c r="B27" s="36">
         <v>2.0713442299999998</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="12">
         <v>4.2925852400000002</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="26">
         <v>1.1482271900000001</v>
       </c>
-      <c r="E27" s="58">
+      <c r="E27" s="36">
         <v>0.76788308999999999</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="12">
         <v>-0.70254135799999995</v>
       </c>
-      <c r="G27" s="40">
+      <c r="G27" s="26">
         <v>3.59060426E-4</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="11">
         <v>2.7571642999999998E-4</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="26">
         <v>-2.5225479899999999E-4</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="11">
         <v>-1.9448398500000001E-4</v>
       </c>
-      <c r="K27" s="40">
+      <c r="K27" s="26">
         <v>1.8622040500000001</v>
       </c>
-      <c r="L27" s="58">
+      <c r="L27" s="36">
         <v>0.38758196700000003</v>
       </c>
-      <c r="M27" s="21">
+      <c r="M27" s="12">
         <v>0.42366399300000002</v>
       </c>
-      <c r="N27" s="5"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="5"/>
-    </row>
-    <row r="33" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="36" t="s">
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="33" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="38"/>
-    </row>
-    <row r="35" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="53" t="s">
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="62"/>
+    </row>
+    <row r="35" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="18" t="s">
+      <c r="B35" s="43"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="F35" s="19"/>
-      <c r="G35" s="54" t="s">
+      <c r="F35" s="44"/>
+      <c r="G35" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="55"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="55"/>
-      <c r="K35" s="54" t="s">
+      <c r="H35" s="33"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L35" s="18" t="s">
+      <c r="L35" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="M35" s="19"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+      <c r="M35" s="44"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36" s="59">
         <v>1</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="43">
         <v>4.4811460500000004</v>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="44">
         <v>4.4988980300000003</v>
       </c>
-      <c r="D36" s="43">
+      <c r="D36" s="56">
         <v>12.1498911</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="43">
         <v>-208.00001700000001</v>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="44">
         <v>200.00001700000001</v>
       </c>
-      <c r="G36" s="43">
+      <c r="G36" s="56">
         <v>2.4944899300000001E-3</v>
       </c>
-      <c r="H36" s="48">
+      <c r="H36" s="53">
         <v>-0.51885394799999995</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="56">
         <v>0.49889802700000002</v>
       </c>
-      <c r="J36" s="48">
+      <c r="J36" s="53">
         <v>-103.850109</v>
       </c>
-      <c r="K36" s="48">
+      <c r="K36" s="53">
         <v>1.5884248400000001</v>
       </c>
-      <c r="L36" s="56">
+      <c r="L36" s="34">
         <v>3.4118965399999999</v>
       </c>
-      <c r="M36" s="57">
+      <c r="M36" s="35">
         <v>3.5503955299999999</v>
       </c>
-      <c r="N36" s="5"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="42"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="51" t="s">
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37" s="46"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="54"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="M37" s="23" t="s">
+      <c r="M37" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="N37" s="5"/>
-    </row>
-    <row r="38" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="44"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="52" t="s">
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="47"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="42">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39" s="46">
         <v>2</v>
       </c>
-      <c r="B39" s="46">
+      <c r="B39" s="51">
         <v>1.3755638800000001</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="50">
         <v>1.3774790299999999</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="48">
         <v>0.14141500700000001</v>
       </c>
-      <c r="E39" s="46">
+      <c r="E39" s="51">
         <v>-3.4734569</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="50">
         <v>-3.49116969</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="48">
         <v>0.89408973999999997</v>
       </c>
-      <c r="H39" s="49">
+      <c r="H39" s="54">
         <v>-3.1055821699999999</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="48">
         <v>-3.1214189999999999</v>
       </c>
-      <c r="J39" s="49">
+      <c r="J39" s="54">
         <v>-12.008476099999999</v>
       </c>
-      <c r="K39" s="48">
+      <c r="K39" s="53">
         <v>3.1397450600000001</v>
       </c>
-      <c r="L39" s="51">
+      <c r="L39" s="29">
         <v>0.36809738600000003</v>
       </c>
-      <c r="M39" s="23">
+      <c r="M39" s="14">
         <v>0.38303066299999999</v>
       </c>
-      <c r="N39" s="5"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="42"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="51" t="s">
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40" s="46"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="54"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="M40" s="23" t="s">
+      <c r="M40" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="N40" s="5"/>
-    </row>
-    <row r="41" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="42"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="50"/>
-      <c r="L41" s="51" t="s">
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="46"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="M41" s="23" t="s">
+      <c r="M41" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="N41" s="5"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A42" s="59">
         <v>3</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="43">
         <v>1.0397276600000001</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C42" s="44">
         <v>1.0399302500000001</v>
       </c>
-      <c r="D42" s="43">
+      <c r="D42" s="56">
         <v>1.5823909799999999E-3</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="43">
         <v>-0.37556404399999999</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="44">
         <v>-0.37747919699999999</v>
       </c>
-      <c r="G42" s="43">
+      <c r="G42" s="56">
         <v>0.89421824500000002</v>
       </c>
-      <c r="H42" s="48">
+      <c r="H42" s="53">
         <v>-0.33583622000000002</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="56">
         <v>-0.33754878500000002</v>
       </c>
-      <c r="J42" s="48">
+      <c r="J42" s="53">
         <v>-0.13983261599999999</v>
       </c>
-      <c r="K42" s="48">
+      <c r="K42" s="53">
         <v>3.1391468599999999</v>
       </c>
-      <c r="L42" s="56">
+      <c r="L42" s="34">
         <v>3.8937854700000003E-2</v>
       </c>
-      <c r="M42" s="57">
+      <c r="M42" s="35">
         <v>4.0517668200000002E-2</v>
       </c>
-      <c r="N42" s="5"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="42"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="51" t="s">
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A43" s="46"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="54"/>
+      <c r="K43" s="54"/>
+      <c r="L43" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="M43" s="23" t="s">
+      <c r="M43" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N43" s="5"/>
-    </row>
-    <row r="44" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="44"/>
-      <c r="B44" s="47"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="52" t="s">
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="47"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="55"/>
+      <c r="L44" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="M44" s="25" t="s">
+      <c r="M44" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="N44" s="5"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="42">
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A45" s="46">
         <v>4</v>
       </c>
-      <c r="B45" s="46">
+      <c r="B45" s="51">
         <v>1.0042032700000001</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="50">
         <v>1.0042247</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="48">
         <v>1.7713407000000001E-5</v>
       </c>
-      <c r="E45" s="46">
+      <c r="E45" s="51">
         <v>-3.9727756400000001E-2</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="50">
         <v>-3.9930344700000002E-2</v>
       </c>
-      <c r="G45" s="30">
+      <c r="G45" s="48">
         <v>0.89419571600000003</v>
       </c>
-      <c r="H45" s="49">
+      <c r="H45" s="54">
         <v>-3.5524389500000003E-2</v>
       </c>
-      <c r="I45" s="30">
+      <c r="I45" s="48">
         <v>-3.5705543200000002E-2</v>
       </c>
-      <c r="J45" s="49">
+      <c r="J45" s="54">
         <v>-1.5646775700000001E-3</v>
       </c>
-      <c r="K45" s="48">
+      <c r="K45" s="53">
         <v>3.13906011</v>
       </c>
-      <c r="L45" s="51">
+      <c r="L45" s="29">
         <v>4.1197950699999996E-3</v>
       </c>
-      <c r="M45" s="23">
+      <c r="M45" s="14">
         <v>4.2869432299999996E-3</v>
       </c>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5"/>
-      <c r="T45" s="5"/>
-      <c r="U45" s="5"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="42"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="49"/>
-      <c r="K46" s="49"/>
-      <c r="L46" s="51" t="s">
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A46" s="46"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="48"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="54"/>
+      <c r="L46" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="M46" s="23" t="s">
+      <c r="M46" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
-      <c r="U46" s="5"/>
-    </row>
-    <row r="47" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="42"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="49"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="51" t="s">
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+    </row>
+    <row r="47" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="46"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="50"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="48"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="55"/>
+      <c r="L47" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="M47" s="23" t="s">
+      <c r="M47" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5"/>
-      <c r="S47" s="5"/>
-      <c r="T47" s="5"/>
-      <c r="U47" s="5"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A48" s="59">
         <v>5</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="43">
         <v>1.0004447000000001</v>
       </c>
-      <c r="C48" s="19">
+      <c r="C48" s="44">
         <v>1.00044697</v>
       </c>
-      <c r="D48" s="43">
+      <c r="D48" s="56">
         <v>1.9827172199999999E-7</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="43">
         <v>-4.20336883E-3</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="44">
         <v>-4.2248035399999996E-3</v>
       </c>
-      <c r="G48" s="43">
+      <c r="G48" s="56">
         <v>0.89418015900000003</v>
       </c>
-      <c r="H48" s="48">
+      <c r="H48" s="53">
         <v>-3.7585689999999998E-3</v>
       </c>
-      <c r="I48" s="43">
+      <c r="I48" s="56">
         <v>-3.7777355000000001E-3</v>
       </c>
-      <c r="J48" s="48">
+      <c r="J48" s="53">
         <v>-1.7515135300000002E-5</v>
       </c>
-      <c r="K48" s="48">
+      <c r="K48" s="53">
         <v>3.1390505700000002</v>
       </c>
-      <c r="L48" s="56">
+      <c r="L48" s="34">
         <v>4.35956037E-4</v>
       </c>
-      <c r="M48" s="57">
+      <c r="M48" s="35">
         <v>4.53643637E-4</v>
       </c>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
-      <c r="U48" s="5"/>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="42"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="49"/>
-      <c r="K49" s="49"/>
-      <c r="L49" s="51" t="s">
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A49" s="46"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="M49" s="23" t="s">
+      <c r="M49" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="5"/>
-      <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
-      <c r="U49" s="5"/>
-    </row>
-    <row r="50" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="44"/>
-      <c r="B50" s="47"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="35"/>
-      <c r="J50" s="50"/>
-      <c r="K50" s="50"/>
-      <c r="L50" s="52" t="s">
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+    </row>
+    <row r="50" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="47"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="49"/>
+      <c r="J50" s="55"/>
+      <c r="K50" s="55"/>
+      <c r="L50" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="M50" s="25" t="s">
+      <c r="M50" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="5"/>
-      <c r="S50" s="5"/>
-      <c r="T50" s="5"/>
-      <c r="U50" s="5"/>
-    </row>
-    <row r="51" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="5"/>
-      <c r="S51" s="5"/>
-      <c r="T51" s="5"/>
-      <c r="U51" s="5"/>
-    </row>
-    <row r="52" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+    </row>
+    <row r="51" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="1"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+    </row>
+    <row r="52" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="37"/>
-      <c r="K52" s="37"/>
-      <c r="L52" s="37"/>
-      <c r="M52" s="38"/>
-    </row>
-    <row r="53" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="39" t="s">
+      <c r="B52" s="61"/>
+      <c r="C52" s="61"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="61"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="61"/>
+      <c r="L52" s="61"/>
+      <c r="M52" s="62"/>
+    </row>
+    <row r="53" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="45" t="s">
+      <c r="B53" s="57"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="F53" s="41"/>
-      <c r="G53" s="40" t="s">
+      <c r="F53" s="58"/>
+      <c r="G53" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="H53" s="20"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="40" t="s">
+      <c r="H53" s="11"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="L53" s="45" t="s">
+      <c r="L53" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="41"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+      <c r="M53" s="58"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A54" s="59">
         <v>1</v>
       </c>
-      <c r="B54" s="18">
+      <c r="B54" s="43">
         <v>2.0710685099999999</v>
       </c>
-      <c r="C54" s="19">
+      <c r="C54" s="44">
         <v>4.2928375000000001</v>
       </c>
-      <c r="D54" s="43">
+      <c r="D54" s="56">
         <v>1.1484216700000001</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="43">
         <v>-42008.010499999997</v>
       </c>
-      <c r="F54" s="19">
+      <c r="F54" s="44">
         <v>4200.00288</v>
       </c>
-      <c r="G54" s="43">
+      <c r="G54" s="56">
         <v>6.9723165900000006E-5</v>
       </c>
-      <c r="H54" s="48">
+      <c r="H54" s="53">
         <v>-2.9289314900000001</v>
       </c>
-      <c r="I54" s="43">
+      <c r="I54" s="56">
         <v>0.292837497</v>
       </c>
-      <c r="J54" s="48">
+      <c r="J54" s="53">
         <v>-44114.851600000002</v>
       </c>
-      <c r="K54" s="43">
+      <c r="K54" s="56">
         <v>1.9206537100000001</v>
       </c>
-      <c r="L54" s="56">
+      <c r="L54" s="34">
         <v>-0.76788308999999999</v>
       </c>
-      <c r="M54" s="57">
+      <c r="M54" s="35">
         <v>0.70254135799999995</v>
       </c>
-      <c r="N54" s="5"/>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="42"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="49"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="51" t="s">
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A55" s="46"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="50"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="48"/>
+      <c r="L55" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="M55" s="12" t="s">
+      <c r="M55" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="44"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="50"/>
-      <c r="I56" s="35"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="35"/>
-      <c r="L56" s="52" t="s">
+    <row r="56" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="47"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="52"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="49"/>
+      <c r="J56" s="55"/>
+      <c r="K56" s="49"/>
+      <c r="L56" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="M56" s="16" t="s">
+      <c r="M56" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="42">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A57" s="46">
         <v>2</v>
       </c>
-      <c r="B57" s="46">
+      <c r="B57" s="51">
         <v>2.07104629</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="50">
         <v>4.2926150400000003</v>
       </c>
-      <c r="D57" s="30">
+      <c r="D57" s="48">
         <v>1.1482841500000001</v>
       </c>
-      <c r="E57" s="46">
+      <c r="E57" s="51">
         <v>-6.1895709799999997E-2</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="50">
         <v>-0.61956688299999996</v>
       </c>
-      <c r="G57" s="30">
+      <c r="G57" s="48">
         <v>3.59060426E-4</v>
       </c>
-      <c r="H57" s="49">
+      <c r="H57" s="54">
         <v>-2.2224299899999998E-5</v>
       </c>
-      <c r="I57" s="30">
+      <c r="I57" s="48">
         <v>-2.22461949E-4</v>
       </c>
-      <c r="J57" s="49">
+      <c r="J57" s="54">
         <v>-1.3752225000000001E-4</v>
       </c>
-      <c r="K57" s="30">
+      <c r="K57" s="48">
         <v>2.7916405499999999</v>
       </c>
-      <c r="L57" s="51">
+      <c r="L57" s="29">
         <v>-0.659865496</v>
       </c>
-      <c r="M57" s="23">
+      <c r="M57" s="14">
         <v>0.67645999899999998</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="42"/>
-      <c r="B58" s="46"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="49"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="51" t="s">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A58" s="46"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="48"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="48"/>
+      <c r="L58" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="M58" s="23" t="s">
+      <c r="M58" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="N58" s="5"/>
-    </row>
-    <row r="59" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="44"/>
-      <c r="B59" s="47"/>
-      <c r="C59" s="28"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="50"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="35"/>
-      <c r="L59" s="52" t="s">
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="47"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="45"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="49"/>
+      <c r="J59" s="55"/>
+      <c r="K59" s="49"/>
+      <c r="L59" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="M59" s="25" t="s">
+      <c r="M59" s="16" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="I54:I56"/>
-    <mergeCell ref="J54:J56"/>
-    <mergeCell ref="K54:K56"/>
-    <mergeCell ref="K57:K59"/>
-    <mergeCell ref="J57:J59"/>
-    <mergeCell ref="I57:I59"/>
-    <mergeCell ref="H57:H59"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="D54:D56"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="J36:J38"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="J42:J44"/>
+    <mergeCell ref="A34:M34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="J45:J47"/>
+    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="H42:H44"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="I45:I47"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="E48:E50"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A47"/>
     <mergeCell ref="K36:K38"/>
     <mergeCell ref="K39:K41"/>
     <mergeCell ref="K42:K44"/>
@@ -6857,58 +6928,31 @@
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="B48:B50"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="E48:E50"/>
-    <mergeCell ref="F48:F50"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="J45:J47"/>
-    <mergeCell ref="I39:I41"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="I45:I47"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="I36:I38"/>
-    <mergeCell ref="J36:J38"/>
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="J42:J44"/>
-    <mergeCell ref="A34:M34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="J54:J56"/>
+    <mergeCell ref="K54:K56"/>
+    <mergeCell ref="K57:K59"/>
+    <mergeCell ref="J57:J59"/>
+    <mergeCell ref="I57:I59"/>
+    <mergeCell ref="H57:H59"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="I54:I56"/>
+    <mergeCell ref="A54:A56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
